--- a/Спектры для SDL/коеф.xlsx
+++ b/Спектры для SDL/коеф.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Chirikalo\ARM_proj\SPRD2_5\Спектры для SDL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F44C9D-785E-4BF0-ACE6-EFD8188CDBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CD530A-9EB2-4143-93B3-9A62928BF8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="3435" windowWidth="21600" windowHeight="11385" xr2:uid="{38CA246D-B91C-43A7-9371-8EF17DAE7119}"/>
+    <workbookView xWindow="-24510" yWindow="1365" windowWidth="21600" windowHeight="11385" xr2:uid="{38CA246D-B91C-43A7-9371-8EF17DAE7119}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -459,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0220CFC-6645-4558-8210-93BEC1627EEE}">
-  <dimension ref="D4:N20"/>
+  <dimension ref="D2:Q20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -468,12 +468,17 @@
     <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="P2">
+        <v>99342</v>
+      </c>
+    </row>
+    <row r="4" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3052</v>
+        <v>33443</v>
       </c>
       <c r="H4" t="s">
         <v>4</v>
@@ -483,22 +488,29 @@
       </c>
       <c r="J4">
         <f>I4*$E$7</f>
-        <v>8.9095692144377321E-4</v>
+        <v>7.4201948012770482E-6</v>
       </c>
       <c r="M4" s="1">
         <v>8.9099999999999997E-4</v>
       </c>
       <c r="N4" s="3">
         <f>M4*$E$6</f>
-        <v>8299.4012640000001</v>
-      </c>
-    </row>
-    <row r="5" spans="4:14" x14ac:dyDescent="0.25">
+        <v>996524.91585899994</v>
+      </c>
+      <c r="P4">
+        <v>986895</v>
+      </c>
+      <c r="Q4">
+        <f>(1/($P$2*$P$2))*P4</f>
+        <v>1.0000118591529948E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>3052</v>
+        <v>33443</v>
       </c>
       <c r="H5" t="s">
         <v>5</v>
@@ -508,23 +520,30 @@
       </c>
       <c r="J5">
         <f t="shared" ref="J5:J20" si="0">I5*$E$7</f>
-        <v>2.6989585498369032E-4</v>
+        <v>2.247785242849801E-6</v>
       </c>
       <c r="M5" s="1">
         <v>2.7E-4</v>
       </c>
       <c r="N5" s="3">
         <f t="shared" ref="N5:N20" si="1">M5*$E$6</f>
-        <v>2514.9700800000001</v>
-      </c>
-    </row>
-    <row r="6" spans="4:14" x14ac:dyDescent="0.25">
+        <v>301977.24722999998</v>
+      </c>
+      <c r="P5">
+        <v>1973790</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q20" si="2">(1/($P$2*$P$2))*P5</f>
+        <v>2.0000237183059896E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>2</v>
       </c>
       <c r="E6">
         <f>E4*E5</f>
-        <v>9314704</v>
+        <v>1118434249</v>
       </c>
       <c r="H6" t="s">
         <v>6</v>
@@ -534,23 +553,30 @@
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>2.8997164053736976E-4</v>
+        <v>2.4149832700625748E-6</v>
       </c>
       <c r="M6" s="1">
         <v>2.9E-4</v>
       </c>
       <c r="N6" s="3">
         <f t="shared" si="1"/>
-        <v>2701.2641600000002</v>
-      </c>
-    </row>
-    <row r="7" spans="4:14" x14ac:dyDescent="0.25">
+        <v>324345.93221</v>
+      </c>
+      <c r="P6">
+        <v>2960685</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>3.0000355774589842E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>3</v>
       </c>
       <c r="E7">
         <f>1/E6</f>
-        <v>1.0735714199828572E-7</v>
+        <v>8.9410709739451118E-10</v>
       </c>
       <c r="H7" t="s">
         <v>7</v>
@@ -560,17 +586,24 @@
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>3.0328392614515715E-4</v>
+        <v>2.5258525501394939E-6</v>
       </c>
       <c r="M7" s="1">
         <v>3.033E-4</v>
       </c>
       <c r="N7" s="3">
         <f t="shared" si="1"/>
-        <v>2825.1497232000002</v>
-      </c>
-    </row>
-    <row r="8" spans="4:14" x14ac:dyDescent="0.25">
+        <v>339221.10772169998</v>
+      </c>
+      <c r="P7">
+        <v>3947580</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>4.0000474366119792E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="4:17" x14ac:dyDescent="0.25">
       <c r="H8" t="s">
         <v>8</v>
       </c>
@@ -579,17 +612,24 @@
       </c>
       <c r="J8">
         <f t="shared" si="0"/>
-        <v>3.3516899731864802E-4</v>
+        <v>2.7914023580656641E-6</v>
       </c>
       <c r="M8" s="1">
         <v>3.3520000000000002E-4</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="1"/>
-        <v>3122.2887808</v>
-      </c>
-    </row>
-    <row r="9" spans="4:14" x14ac:dyDescent="0.25">
+        <v>374899.16026480001</v>
+      </c>
+      <c r="P8">
+        <v>4934475</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>5.0000592957649736E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="4:17" x14ac:dyDescent="0.25">
       <c r="H9" t="s">
         <v>9</v>
       </c>
@@ -598,17 +638,24 @@
       </c>
       <c r="J9">
         <f t="shared" si="0"/>
-        <v>2.3511214097624573E-4</v>
+        <v>1.9580945432939795E-6</v>
       </c>
       <c r="M9" s="1">
         <v>2.352E-4</v>
       </c>
       <c r="N9" s="3">
         <f t="shared" si="1"/>
-        <v>2190.8183807999999</v>
-      </c>
-    </row>
-    <row r="10" spans="4:14" x14ac:dyDescent="0.25">
+        <v>263055.73536479997</v>
+      </c>
+      <c r="P9">
+        <v>5921370</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>6.0000711549179685E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="4:17" x14ac:dyDescent="0.25">
       <c r="H10" t="s">
         <v>10</v>
       </c>
@@ -617,17 +664,24 @@
       </c>
       <c r="J10">
         <f t="shared" si="0"/>
-        <v>5.2239985296365836E-4</v>
+        <v>4.3507251359216912E-6</v>
       </c>
       <c r="M10" s="1">
         <v>5.2249999999999996E-4</v>
       </c>
       <c r="N10" s="3">
         <f t="shared" si="1"/>
-        <v>4866.9328399999995</v>
-      </c>
-    </row>
-    <row r="11" spans="4:14" x14ac:dyDescent="0.25">
+        <v>584381.89510249998</v>
+      </c>
+      <c r="P10">
+        <v>6908265</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>7.0000830140709634E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="H11" t="s">
         <v>11</v>
       </c>
@@ -636,17 +690,24 @@
       </c>
       <c r="J11">
         <f t="shared" si="0"/>
-        <v>8.2987070764674862E-4</v>
+        <v>6.9114478628595714E-6</v>
       </c>
       <c r="M11" s="1">
         <v>8.2989999999999995E-4</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="1"/>
-        <v>7730.2728496</v>
-      </c>
-    </row>
-    <row r="12" spans="4:14" x14ac:dyDescent="0.25">
+        <v>928188.58324509999</v>
+      </c>
+      <c r="P11">
+        <v>7895160</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>8.0000948732239583E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="H12" t="s">
         <v>12</v>
       </c>
@@ -655,17 +716,24 @@
       </c>
       <c r="J12">
         <f t="shared" si="0"/>
-        <v>1.2729336326736738E-3</v>
+        <v>1.0601427853806719E-5</v>
       </c>
       <c r="M12" s="1">
         <v>1.273E-3</v>
       </c>
       <c r="N12" s="3">
         <f t="shared" si="1"/>
-        <v>11857.618192</v>
-      </c>
-    </row>
-    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
+        <v>1423766.7989769999</v>
+      </c>
+      <c r="P12">
+        <v>8882055</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="2"/>
+        <v>9.0001067323769533E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="H13" t="s">
         <v>13</v>
       </c>
@@ -674,17 +742,24 @@
       </c>
       <c r="J13">
         <f t="shared" si="0"/>
-        <v>1.8649009136522212E-3</v>
+        <v>1.5531534388840054E-5</v>
       </c>
       <c r="M13" s="1">
         <v>1.8649999999999999E-3</v>
       </c>
       <c r="N13" s="3">
         <f t="shared" si="1"/>
-        <v>17371.92296</v>
-      </c>
-    </row>
-    <row r="14" spans="4:14" x14ac:dyDescent="0.25">
+        <v>2085879.874385</v>
+      </c>
+      <c r="P13">
+        <v>9868950</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="2"/>
+        <v>1.0000118591529947E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="4:17" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
         <v>14</v>
       </c>
@@ -693,17 +768,24 @@
       </c>
       <c r="J14">
         <f t="shared" si="0"/>
-        <v>2.5999752649144836E-3</v>
+        <v>2.1653485684700273E-5</v>
       </c>
       <c r="M14" s="1">
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="N14" s="3">
         <f t="shared" si="1"/>
-        <v>24218.2304</v>
-      </c>
-    </row>
-    <row r="15" spans="4:14" x14ac:dyDescent="0.25">
+        <v>2907929.0474</v>
+      </c>
+      <c r="P14">
+        <v>10855845</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="2"/>
+        <v>1.1000130450682943E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="4:17" x14ac:dyDescent="0.25">
       <c r="H15" t="s">
         <v>15</v>
       </c>
@@ -712,17 +794,24 @@
       </c>
       <c r="J15">
         <f t="shared" si="0"/>
-        <v>3.6399438994518776E-3</v>
+        <v>3.0314701137160901E-5</v>
       </c>
       <c r="M15" s="1">
         <v>3.64E-3</v>
       </c>
       <c r="N15" s="3">
         <f t="shared" si="1"/>
-        <v>33905.522559999998</v>
-      </c>
-    </row>
-    <row r="16" spans="4:14" x14ac:dyDescent="0.25">
+        <v>4071100.6663600001</v>
+      </c>
+      <c r="P15">
+        <v>11842740</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="2"/>
+        <v>1.2000142309835937E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="4:17" x14ac:dyDescent="0.25">
       <c r="H16" t="s">
         <v>16</v>
       </c>
@@ -731,17 +820,24 @@
       </c>
       <c r="J16">
         <f t="shared" si="0"/>
-        <v>4.8599504611203962E-3</v>
+        <v>4.0475334191952128E-5</v>
       </c>
       <c r="M16" s="1">
         <v>4.8599999999999997E-3</v>
       </c>
       <c r="N16" s="3">
         <f t="shared" si="1"/>
-        <v>45269.461439999999</v>
-      </c>
-    </row>
-    <row r="17" spans="8:14" x14ac:dyDescent="0.25">
+        <v>5435590.4501399994</v>
+      </c>
+      <c r="P16">
+        <v>12829635</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="2"/>
+        <v>1.3000154168988933E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H17" t="s">
         <v>17</v>
       </c>
@@ -750,17 +846,24 @@
       </c>
       <c r="J17">
         <f t="shared" si="0"/>
-        <v>6.8499224452006208E-3</v>
+        <v>5.7048503349256786E-5</v>
       </c>
       <c r="M17" s="1">
         <v>6.8500000000000002E-3</v>
       </c>
       <c r="N17" s="3">
         <f t="shared" si="1"/>
-        <v>63805.722399999999</v>
-      </c>
-    </row>
-    <row r="18" spans="8:14" x14ac:dyDescent="0.25">
+        <v>7661274.6056500003</v>
+      </c>
+      <c r="P17">
+        <v>13816530</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="2"/>
+        <v>1.4000166028141927E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H18" t="s">
         <v>18</v>
       </c>
@@ -769,17 +872,24 @@
       </c>
       <c r="J18">
         <f t="shared" si="0"/>
-        <v>7.9099668652916934E-3</v>
+        <v>6.5876916828930189E-5</v>
       </c>
       <c r="M18" s="1">
         <v>7.9100000000000004E-3</v>
       </c>
       <c r="N18" s="3">
         <f t="shared" si="1"/>
-        <v>73679.308640000003</v>
-      </c>
-    </row>
-    <row r="19" spans="8:14" x14ac:dyDescent="0.25">
+        <v>8846814.9095900003</v>
+      </c>
+      <c r="P18">
+        <v>14803425</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="2"/>
+        <v>1.5000177887294923E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H19" t="s">
         <v>19</v>
       </c>
@@ -788,17 +898,24 @@
       </c>
       <c r="J19">
         <f t="shared" si="0"/>
-        <v>1.1999951904000385E-2</v>
+        <v>9.9939714918368883E-5</v>
       </c>
       <c r="M19" s="2">
         <v>1.2E-2</v>
       </c>
       <c r="N19" s="3">
         <f t="shared" si="1"/>
-        <v>111776.448</v>
-      </c>
-    </row>
-    <row r="20" spans="8:14" x14ac:dyDescent="0.25">
+        <v>13421210.988</v>
+      </c>
+      <c r="P19">
+        <v>15790320</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="2"/>
+        <v>1.6000189746447917E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H20" t="s">
         <v>20</v>
       </c>
@@ -807,14 +924,21 @@
       </c>
       <c r="J20">
         <f t="shared" si="0"/>
-        <v>1.500004723714248E-2</v>
+        <v>1.2492553775505849E-4</v>
       </c>
       <c r="M20" s="2">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N20" s="3">
         <f t="shared" si="1"/>
-        <v>139720.56</v>
+        <v>16776513.734999999</v>
+      </c>
+      <c r="P20">
+        <v>16777215</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="2"/>
+        <v>1.7000201605600913E-3</v>
       </c>
     </row>
   </sheetData>

--- a/Спектры для SDL/коеф.xlsx
+++ b/Спектры для SDL/коеф.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Chirikalo\ARM_proj\SPRD2_5\Спектры для SDL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CD530A-9EB2-4143-93B3-9A62928BF8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7029C41-A8A8-44C2-AC62-C4A2323E4F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24510" yWindow="1365" windowWidth="21600" windowHeight="11385" xr2:uid="{38CA246D-B91C-43A7-9371-8EF17DAE7119}"/>
   </bookViews>
@@ -459,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0220CFC-6645-4558-8210-93BEC1627EEE}">
-  <dimension ref="D2:Q20"/>
+  <dimension ref="D2:R20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -468,12 +468,16 @@
     <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:18" x14ac:dyDescent="0.25">
       <c r="P2">
         <v>99342</v>
       </c>
-    </row>
-    <row r="4" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R2" t="str">
+        <f xml:space="preserve"> DEC2HEX(P2)</f>
+        <v>1840E</v>
+      </c>
+    </row>
+    <row r="4" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>0</v>
       </c>
@@ -504,8 +508,12 @@
         <f>(1/($P$2*$P$2))*P4</f>
         <v>1.0000118591529948E-4</v>
       </c>
-    </row>
-    <row r="5" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R4" t="str">
+        <f xml:space="preserve"> DEC2HEX(P4)</f>
+        <v>F0F0F</v>
+      </c>
+    </row>
+    <row r="5" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>1</v>
       </c>
@@ -536,8 +544,12 @@
         <f t="shared" ref="Q5:Q20" si="2">(1/($P$2*$P$2))*P5</f>
         <v>2.0000237183059896E-4</v>
       </c>
-    </row>
-    <row r="6" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R5" t="str">
+        <f t="shared" ref="R5:R20" si="3" xml:space="preserve"> DEC2HEX(P5)</f>
+        <v>1E1E1E</v>
+      </c>
+    </row>
+    <row r="6" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>2</v>
       </c>
@@ -569,8 +581,12 @@
         <f t="shared" si="2"/>
         <v>3.0000355774589842E-4</v>
       </c>
-    </row>
-    <row r="7" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R6" t="str">
+        <f t="shared" si="3"/>
+        <v>2D2D2D</v>
+      </c>
+    </row>
+    <row r="7" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>3</v>
       </c>
@@ -602,8 +618,12 @@
         <f t="shared" si="2"/>
         <v>4.0000474366119792E-4</v>
       </c>
-    </row>
-    <row r="8" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R7" t="str">
+        <f t="shared" si="3"/>
+        <v>3C3C3C</v>
+      </c>
+    </row>
+    <row r="8" spans="4:18" x14ac:dyDescent="0.25">
       <c r="H8" t="s">
         <v>8</v>
       </c>
@@ -628,8 +648,12 @@
         <f t="shared" si="2"/>
         <v>5.0000592957649736E-4</v>
       </c>
-    </row>
-    <row r="9" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R8" t="str">
+        <f t="shared" si="3"/>
+        <v>4B4B4B</v>
+      </c>
+    </row>
+    <row r="9" spans="4:18" x14ac:dyDescent="0.25">
       <c r="H9" t="s">
         <v>9</v>
       </c>
@@ -654,8 +678,12 @@
         <f t="shared" si="2"/>
         <v>6.0000711549179685E-4</v>
       </c>
-    </row>
-    <row r="10" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R9" t="str">
+        <f t="shared" si="3"/>
+        <v>5A5A5A</v>
+      </c>
+    </row>
+    <row r="10" spans="4:18" x14ac:dyDescent="0.25">
       <c r="H10" t="s">
         <v>10</v>
       </c>
@@ -680,8 +708,12 @@
         <f t="shared" si="2"/>
         <v>7.0000830140709634E-4</v>
       </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R10" t="str">
+        <f t="shared" si="3"/>
+        <v>696969</v>
+      </c>
+    </row>
+    <row r="11" spans="4:18" x14ac:dyDescent="0.25">
       <c r="H11" t="s">
         <v>11</v>
       </c>
@@ -706,8 +738,12 @@
         <f t="shared" si="2"/>
         <v>8.0000948732239583E-4</v>
       </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R11" t="str">
+        <f t="shared" si="3"/>
+        <v>787878</v>
+      </c>
+    </row>
+    <row r="12" spans="4:18" x14ac:dyDescent="0.25">
       <c r="H12" t="s">
         <v>12</v>
       </c>
@@ -732,8 +768,12 @@
         <f t="shared" si="2"/>
         <v>9.0001067323769533E-4</v>
       </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R12" t="str">
+        <f t="shared" si="3"/>
+        <v>878787</v>
+      </c>
+    </row>
+    <row r="13" spans="4:18" x14ac:dyDescent="0.25">
       <c r="H13" t="s">
         <v>13</v>
       </c>
@@ -758,8 +798,12 @@
         <f t="shared" si="2"/>
         <v>1.0000118591529947E-3</v>
       </c>
-    </row>
-    <row r="14" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R13" t="str">
+        <f t="shared" si="3"/>
+        <v>969696</v>
+      </c>
+    </row>
+    <row r="14" spans="4:18" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
         <v>14</v>
       </c>
@@ -784,8 +828,12 @@
         <f t="shared" si="2"/>
         <v>1.1000130450682943E-3</v>
       </c>
-    </row>
-    <row r="15" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R14" t="str">
+        <f t="shared" si="3"/>
+        <v>A5A5A5</v>
+      </c>
+    </row>
+    <row r="15" spans="4:18" x14ac:dyDescent="0.25">
       <c r="H15" t="s">
         <v>15</v>
       </c>
@@ -810,8 +858,12 @@
         <f t="shared" si="2"/>
         <v>1.2000142309835937E-3</v>
       </c>
-    </row>
-    <row r="16" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R15" t="str">
+        <f t="shared" si="3"/>
+        <v>B4B4B4</v>
+      </c>
+    </row>
+    <row r="16" spans="4:18" x14ac:dyDescent="0.25">
       <c r="H16" t="s">
         <v>16</v>
       </c>
@@ -836,8 +888,12 @@
         <f t="shared" si="2"/>
         <v>1.3000154168988933E-3</v>
       </c>
-    </row>
-    <row r="17" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="R16" t="str">
+        <f t="shared" si="3"/>
+        <v>C3C3C3</v>
+      </c>
+    </row>
+    <row r="17" spans="8:18" x14ac:dyDescent="0.25">
       <c r="H17" t="s">
         <v>17</v>
       </c>
@@ -862,8 +918,12 @@
         <f t="shared" si="2"/>
         <v>1.4000166028141927E-3</v>
       </c>
-    </row>
-    <row r="18" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="R17" t="str">
+        <f t="shared" si="3"/>
+        <v>D2D2D2</v>
+      </c>
+    </row>
+    <row r="18" spans="8:18" x14ac:dyDescent="0.25">
       <c r="H18" t="s">
         <v>18</v>
       </c>
@@ -888,8 +948,12 @@
         <f t="shared" si="2"/>
         <v>1.5000177887294923E-3</v>
       </c>
-    </row>
-    <row r="19" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="R18" t="str">
+        <f t="shared" si="3"/>
+        <v>E1E1E1</v>
+      </c>
+    </row>
+    <row r="19" spans="8:18" x14ac:dyDescent="0.25">
       <c r="H19" t="s">
         <v>19</v>
       </c>
@@ -914,8 +978,12 @@
         <f t="shared" si="2"/>
         <v>1.6000189746447917E-3</v>
       </c>
-    </row>
-    <row r="20" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="R19" t="str">
+        <f t="shared" si="3"/>
+        <v>F0F0F0</v>
+      </c>
+    </row>
+    <row r="20" spans="8:18" x14ac:dyDescent="0.25">
       <c r="H20" t="s">
         <v>20</v>
       </c>
@@ -939,6 +1007,10 @@
       <c r="Q20">
         <f t="shared" si="2"/>
         <v>1.7000201605600913E-3</v>
+      </c>
+      <c r="R20" t="str">
+        <f t="shared" si="3"/>
+        <v>FFFFFF</v>
       </c>
     </row>
   </sheetData>

--- a/Спектры для SDL/коеф.xlsx
+++ b/Спектры для SDL/коеф.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Chirikalo\ARM_proj\SPRD2_5\Спектры для SDL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7029C41-A8A8-44C2-AC62-C4A2323E4F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CDE8DC-E99B-4420-9BF1-7C155ADE0CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24510" yWindow="1365" windowWidth="21600" windowHeight="11385" xr2:uid="{38CA246D-B91C-43A7-9371-8EF17DAE7119}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" xr2:uid="{38CA246D-B91C-43A7-9371-8EF17DAE7119}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -459,16 +459,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0220CFC-6645-4558-8210-93BEC1627EEE}">
-  <dimension ref="D2:R20"/>
+  <dimension ref="D2:T20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.140625" style="2"/>
     <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:20" x14ac:dyDescent="0.25">
       <c r="P2">
         <v>99342</v>
       </c>
@@ -476,8 +478,16 @@
         <f xml:space="preserve"> DEC2HEX(P2)</f>
         <v>1840E</v>
       </c>
-    </row>
-    <row r="4" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="S2">
+        <f>P2*P2</f>
+        <v>9868832964</v>
+      </c>
+      <c r="T2">
+        <f>1/S2</f>
+        <v>1.0132910382087201E-10</v>
+      </c>
+    </row>
+    <row r="4" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>0</v>
       </c>
@@ -512,8 +522,12 @@
         <f xml:space="preserve"> DEC2HEX(P4)</f>
         <v>F0F0F</v>
       </c>
-    </row>
-    <row r="5" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="T4">
+        <f>P4*$T$2</f>
+        <v>1.0000118591529948E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>1</v>
       </c>
@@ -548,8 +562,12 @@
         <f t="shared" ref="R5:R20" si="3" xml:space="preserve"> DEC2HEX(P5)</f>
         <v>1E1E1E</v>
       </c>
-    </row>
-    <row r="6" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="T5">
+        <f t="shared" ref="T5:T20" si="4">P5*$T$2</f>
+        <v>2.0000237183059896E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>2</v>
       </c>
@@ -585,8 +603,12 @@
         <f t="shared" si="3"/>
         <v>2D2D2D</v>
       </c>
-    </row>
-    <row r="7" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>3.0000355774589842E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>3</v>
       </c>
@@ -622,8 +644,12 @@
         <f t="shared" si="3"/>
         <v>3C3C3C</v>
       </c>
-    </row>
-    <row r="8" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>4.0000474366119792E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="4:20" x14ac:dyDescent="0.25">
       <c r="H8" t="s">
         <v>8</v>
       </c>
@@ -652,8 +678,12 @@
         <f t="shared" si="3"/>
         <v>4B4B4B</v>
       </c>
-    </row>
-    <row r="9" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>5.0000592957649736E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="4:20" x14ac:dyDescent="0.25">
       <c r="H9" t="s">
         <v>9</v>
       </c>
@@ -682,8 +712,12 @@
         <f t="shared" si="3"/>
         <v>5A5A5A</v>
       </c>
-    </row>
-    <row r="10" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>6.0000711549179685E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="4:20" x14ac:dyDescent="0.25">
       <c r="H10" t="s">
         <v>10</v>
       </c>
@@ -712,8 +746,12 @@
         <f t="shared" si="3"/>
         <v>696969</v>
       </c>
-    </row>
-    <row r="11" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>7.0000830140709634E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="4:20" x14ac:dyDescent="0.25">
       <c r="H11" t="s">
         <v>11</v>
       </c>
@@ -742,8 +780,12 @@
         <f t="shared" si="3"/>
         <v>787878</v>
       </c>
-    </row>
-    <row r="12" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>8.0000948732239583E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="4:20" x14ac:dyDescent="0.25">
       <c r="H12" t="s">
         <v>12</v>
       </c>
@@ -772,8 +814,12 @@
         <f t="shared" si="3"/>
         <v>878787</v>
       </c>
-    </row>
-    <row r="13" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="T12">
+        <f t="shared" si="4"/>
+        <v>9.0001067323769533E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="4:20" x14ac:dyDescent="0.25">
       <c r="H13" t="s">
         <v>13</v>
       </c>
@@ -802,8 +848,12 @@
         <f t="shared" si="3"/>
         <v>969696</v>
       </c>
-    </row>
-    <row r="14" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="T13">
+        <f t="shared" si="4"/>
+        <v>1.0000118591529947E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="4:20" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
         <v>14</v>
       </c>
@@ -832,8 +882,12 @@
         <f t="shared" si="3"/>
         <v>A5A5A5</v>
       </c>
-    </row>
-    <row r="15" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="T14">
+        <f t="shared" si="4"/>
+        <v>1.1000130450682943E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="4:20" x14ac:dyDescent="0.25">
       <c r="H15" t="s">
         <v>15</v>
       </c>
@@ -862,8 +916,12 @@
         <f t="shared" si="3"/>
         <v>B4B4B4</v>
       </c>
-    </row>
-    <row r="16" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="T15">
+        <f t="shared" si="4"/>
+        <v>1.2000142309835937E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="4:20" x14ac:dyDescent="0.25">
       <c r="H16" t="s">
         <v>16</v>
       </c>
@@ -892,8 +950,12 @@
         <f t="shared" si="3"/>
         <v>C3C3C3</v>
       </c>
-    </row>
-    <row r="17" spans="8:18" x14ac:dyDescent="0.25">
+      <c r="T16">
+        <f t="shared" si="4"/>
+        <v>1.3000154168988933E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="8:20" x14ac:dyDescent="0.25">
       <c r="H17" t="s">
         <v>17</v>
       </c>
@@ -922,8 +984,12 @@
         <f t="shared" si="3"/>
         <v>D2D2D2</v>
       </c>
-    </row>
-    <row r="18" spans="8:18" x14ac:dyDescent="0.25">
+      <c r="T17">
+        <f t="shared" si="4"/>
+        <v>1.4000166028141927E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="8:20" x14ac:dyDescent="0.25">
       <c r="H18" t="s">
         <v>18</v>
       </c>
@@ -952,8 +1018,12 @@
         <f t="shared" si="3"/>
         <v>E1E1E1</v>
       </c>
-    </row>
-    <row r="19" spans="8:18" x14ac:dyDescent="0.25">
+      <c r="T18">
+        <f t="shared" si="4"/>
+        <v>1.5000177887294923E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="8:20" x14ac:dyDescent="0.25">
       <c r="H19" t="s">
         <v>19</v>
       </c>
@@ -982,8 +1052,12 @@
         <f t="shared" si="3"/>
         <v>F0F0F0</v>
       </c>
-    </row>
-    <row r="20" spans="8:18" x14ac:dyDescent="0.25">
+      <c r="T19">
+        <f t="shared" si="4"/>
+        <v>1.6000189746447917E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="8:20" x14ac:dyDescent="0.25">
       <c r="H20" t="s">
         <v>20</v>
       </c>
@@ -1011,6 +1085,10 @@
       <c r="R20" t="str">
         <f t="shared" si="3"/>
         <v>FFFFFF</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="4"/>
+        <v>1.7000201605600913E-3</v>
       </c>
     </row>
   </sheetData>

--- a/Спектры для SDL/коеф.xlsx
+++ b/Спектры для SDL/коеф.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Chirikalo\ARM_proj\SPRD2_5\Спектры для SDL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARM_proj\SPRD2_5\Спектры для SDL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CD530A-9EB2-4143-93B3-9A62928BF8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13778A47-8C77-48C0-B848-AE7778777115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24510" yWindow="1365" windowWidth="21600" windowHeight="11385" xr2:uid="{38CA246D-B91C-43A7-9371-8EF17DAE7119}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="15576" windowHeight="11904" xr2:uid="{38CA246D-B91C-43A7-9371-8EF17DAE7119}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -140,10 +140,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -163,9 +162,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -203,7 +202,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -309,7 +308,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -451,7 +450,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -459,21 +458,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0220CFC-6645-4558-8210-93BEC1627EEE}">
-  <dimension ref="D2:Q20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="D2:R20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="2"/>
-    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375"/>
+    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:18" x14ac:dyDescent="0.3">
       <c r="P2">
         <v>99342</v>
       </c>
-    </row>
-    <row r="4" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R2" t="str">
+        <f xml:space="preserve"> DEC2HEX(P2)</f>
+        <v>1840E</v>
+      </c>
+    </row>
+    <row r="3" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f>P2*P2</f>
+        <v>9868832964</v>
+      </c>
+      <c r="R3" t="str">
+        <f xml:space="preserve"> DEC2HEX(Q3)</f>
+        <v>24C3A70C4</v>
+      </c>
+    </row>
+    <row r="4" spans="4:18" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>0</v>
       </c>
@@ -493,7 +508,7 @@
       <c r="M4" s="1">
         <v>8.9099999999999997E-4</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <f>M4*$E$6</f>
         <v>996524.91585899994</v>
       </c>
@@ -504,8 +519,12 @@
         <f>(1/($P$2*$P$2))*P4</f>
         <v>1.0000118591529948E-4</v>
       </c>
-    </row>
-    <row r="5" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R4" t="str">
+        <f>DEC2HEX(P4)</f>
+        <v>F0F0F</v>
+      </c>
+    </row>
+    <row r="5" spans="4:18" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>1</v>
       </c>
@@ -525,7 +544,7 @@
       <c r="M5" s="1">
         <v>2.7E-4</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <f t="shared" ref="N5:N20" si="1">M5*$E$6</f>
         <v>301977.24722999998</v>
       </c>
@@ -536,8 +555,12 @@
         <f t="shared" ref="Q5:Q20" si="2">(1/($P$2*$P$2))*P5</f>
         <v>2.0000237183059896E-4</v>
       </c>
-    </row>
-    <row r="6" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R5" t="str">
+        <f t="shared" ref="R5:R20" si="3">DEC2HEX(P5)</f>
+        <v>1E1E1E</v>
+      </c>
+    </row>
+    <row r="6" spans="4:18" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>2</v>
       </c>
@@ -558,7 +581,7 @@
       <c r="M6" s="1">
         <v>2.9E-4</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="2">
         <f t="shared" si="1"/>
         <v>324345.93221</v>
       </c>
@@ -569,8 +592,12 @@
         <f t="shared" si="2"/>
         <v>3.0000355774589842E-4</v>
       </c>
-    </row>
-    <row r="7" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R6" t="str">
+        <f t="shared" si="3"/>
+        <v>2D2D2D</v>
+      </c>
+    </row>
+    <row r="7" spans="4:18" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>3</v>
       </c>
@@ -591,7 +618,7 @@
       <c r="M7" s="1">
         <v>3.033E-4</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="2">
         <f t="shared" si="1"/>
         <v>339221.10772169998</v>
       </c>
@@ -602,8 +629,12 @@
         <f t="shared" si="2"/>
         <v>4.0000474366119792E-4</v>
       </c>
-    </row>
-    <row r="8" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R7" t="str">
+        <f t="shared" si="3"/>
+        <v>3C3C3C</v>
+      </c>
+    </row>
+    <row r="8" spans="4:18" x14ac:dyDescent="0.3">
       <c r="H8" t="s">
         <v>8</v>
       </c>
@@ -617,7 +648,7 @@
       <c r="M8" s="1">
         <v>3.3520000000000002E-4</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="2">
         <f t="shared" si="1"/>
         <v>374899.16026480001</v>
       </c>
@@ -628,8 +659,12 @@
         <f t="shared" si="2"/>
         <v>5.0000592957649736E-4</v>
       </c>
-    </row>
-    <row r="9" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R8" t="str">
+        <f t="shared" si="3"/>
+        <v>4B4B4B</v>
+      </c>
+    </row>
+    <row r="9" spans="4:18" x14ac:dyDescent="0.3">
       <c r="H9" t="s">
         <v>9</v>
       </c>
@@ -643,7 +678,7 @@
       <c r="M9" s="1">
         <v>2.352E-4</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="2">
         <f t="shared" si="1"/>
         <v>263055.73536479997</v>
       </c>
@@ -654,8 +689,12 @@
         <f t="shared" si="2"/>
         <v>6.0000711549179685E-4</v>
       </c>
-    </row>
-    <row r="10" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R9" t="str">
+        <f t="shared" si="3"/>
+        <v>5A5A5A</v>
+      </c>
+    </row>
+    <row r="10" spans="4:18" x14ac:dyDescent="0.3">
       <c r="H10" t="s">
         <v>10</v>
       </c>
@@ -669,7 +708,7 @@
       <c r="M10" s="1">
         <v>5.2249999999999996E-4</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="2">
         <f t="shared" si="1"/>
         <v>584381.89510249998</v>
       </c>
@@ -680,8 +719,12 @@
         <f t="shared" si="2"/>
         <v>7.0000830140709634E-4</v>
       </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R10" t="str">
+        <f t="shared" si="3"/>
+        <v>696969</v>
+      </c>
+    </row>
+    <row r="11" spans="4:18" x14ac:dyDescent="0.3">
       <c r="H11" t="s">
         <v>11</v>
       </c>
@@ -695,7 +738,7 @@
       <c r="M11" s="1">
         <v>8.2989999999999995E-4</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="2">
         <f t="shared" si="1"/>
         <v>928188.58324509999</v>
       </c>
@@ -706,8 +749,12 @@
         <f t="shared" si="2"/>
         <v>8.0000948732239583E-4</v>
       </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R11" t="str">
+        <f t="shared" si="3"/>
+        <v>787878</v>
+      </c>
+    </row>
+    <row r="12" spans="4:18" x14ac:dyDescent="0.3">
       <c r="H12" t="s">
         <v>12</v>
       </c>
@@ -721,7 +768,7 @@
       <c r="M12" s="1">
         <v>1.273E-3</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="2">
         <f t="shared" si="1"/>
         <v>1423766.7989769999</v>
       </c>
@@ -732,8 +779,12 @@
         <f t="shared" si="2"/>
         <v>9.0001067323769533E-4</v>
       </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R12" t="str">
+        <f t="shared" si="3"/>
+        <v>878787</v>
+      </c>
+    </row>
+    <row r="13" spans="4:18" x14ac:dyDescent="0.3">
       <c r="H13" t="s">
         <v>13</v>
       </c>
@@ -747,7 +798,7 @@
       <c r="M13" s="1">
         <v>1.8649999999999999E-3</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="2">
         <f t="shared" si="1"/>
         <v>2085879.874385</v>
       </c>
@@ -758,8 +809,12 @@
         <f t="shared" si="2"/>
         <v>1.0000118591529947E-3</v>
       </c>
-    </row>
-    <row r="14" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R13" t="str">
+        <f t="shared" si="3"/>
+        <v>969696</v>
+      </c>
+    </row>
+    <row r="14" spans="4:18" x14ac:dyDescent="0.3">
       <c r="H14" t="s">
         <v>14</v>
       </c>
@@ -773,7 +828,7 @@
       <c r="M14" s="1">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="2">
         <f t="shared" si="1"/>
         <v>2907929.0474</v>
       </c>
@@ -784,8 +839,12 @@
         <f t="shared" si="2"/>
         <v>1.1000130450682943E-3</v>
       </c>
-    </row>
-    <row r="15" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R14" t="str">
+        <f t="shared" si="3"/>
+        <v>A5A5A5</v>
+      </c>
+    </row>
+    <row r="15" spans="4:18" x14ac:dyDescent="0.3">
       <c r="H15" t="s">
         <v>15</v>
       </c>
@@ -799,7 +858,7 @@
       <c r="M15" s="1">
         <v>3.64E-3</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="2">
         <f t="shared" si="1"/>
         <v>4071100.6663600001</v>
       </c>
@@ -810,8 +869,12 @@
         <f t="shared" si="2"/>
         <v>1.2000142309835937E-3</v>
       </c>
-    </row>
-    <row r="16" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R15" t="str">
+        <f t="shared" si="3"/>
+        <v>B4B4B4</v>
+      </c>
+    </row>
+    <row r="16" spans="4:18" x14ac:dyDescent="0.3">
       <c r="H16" t="s">
         <v>16</v>
       </c>
@@ -825,7 +888,7 @@
       <c r="M16" s="1">
         <v>4.8599999999999997E-3</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="2">
         <f t="shared" si="1"/>
         <v>5435590.4501399994</v>
       </c>
@@ -836,8 +899,12 @@
         <f t="shared" si="2"/>
         <v>1.3000154168988933E-3</v>
       </c>
-    </row>
-    <row r="17" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="R16" t="str">
+        <f t="shared" si="3"/>
+        <v>C3C3C3</v>
+      </c>
+    </row>
+    <row r="17" spans="8:18" x14ac:dyDescent="0.3">
       <c r="H17" t="s">
         <v>17</v>
       </c>
@@ -851,7 +918,7 @@
       <c r="M17" s="1">
         <v>6.8500000000000002E-3</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="2">
         <f t="shared" si="1"/>
         <v>7661274.6056500003</v>
       </c>
@@ -862,8 +929,12 @@
         <f t="shared" si="2"/>
         <v>1.4000166028141927E-3</v>
       </c>
-    </row>
-    <row r="18" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="R17" t="str">
+        <f t="shared" si="3"/>
+        <v>D2D2D2</v>
+      </c>
+    </row>
+    <row r="18" spans="8:18" x14ac:dyDescent="0.3">
       <c r="H18" t="s">
         <v>18</v>
       </c>
@@ -877,7 +948,7 @@
       <c r="M18" s="1">
         <v>7.9100000000000004E-3</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="2">
         <f t="shared" si="1"/>
         <v>8846814.9095900003</v>
       </c>
@@ -888,22 +959,26 @@
         <f t="shared" si="2"/>
         <v>1.5000177887294923E-3</v>
       </c>
-    </row>
-    <row r="19" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="R18" t="str">
+        <f t="shared" si="3"/>
+        <v>E1E1E1</v>
+      </c>
+    </row>
+    <row r="19" spans="8:18" x14ac:dyDescent="0.3">
       <c r="H19" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="2">
         <v>111776</v>
       </c>
       <c r="J19">
         <f t="shared" si="0"/>
         <v>9.9939714918368883E-5</v>
       </c>
-      <c r="M19" s="2">
+      <c r="M19">
         <v>1.2E-2</v>
       </c>
-      <c r="N19" s="3">
+      <c r="N19" s="2">
         <f t="shared" si="1"/>
         <v>13421210.988</v>
       </c>
@@ -914,8 +989,12 @@
         <f t="shared" si="2"/>
         <v>1.6000189746447917E-3</v>
       </c>
-    </row>
-    <row r="20" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="R19" t="str">
+        <f t="shared" si="3"/>
+        <v>F0F0F0</v>
+      </c>
+    </row>
+    <row r="20" spans="8:18" x14ac:dyDescent="0.3">
       <c r="H20" t="s">
         <v>20</v>
       </c>
@@ -926,10 +1005,10 @@
         <f t="shared" si="0"/>
         <v>1.2492553775505849E-4</v>
       </c>
-      <c r="M20" s="2">
+      <c r="M20">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="2">
         <f t="shared" si="1"/>
         <v>16776513.734999999</v>
       </c>
@@ -939,6 +1018,10 @@
       <c r="Q20">
         <f t="shared" si="2"/>
         <v>1.7000201605600913E-3</v>
+      </c>
+      <c r="R20" t="str">
+        <f t="shared" si="3"/>
+        <v>FFFFFF</v>
       </c>
     </row>
   </sheetData>
